--- a/ProGit/Commands.xlsx
+++ b/ProGit/Commands.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git_projects\fullGit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Git\ProGit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A44D056-D840-47B2-AE9C-EFF2139DA2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE89269-A775-4460-B8A3-E3C6398F6D57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="2505" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="327">
   <si>
     <t>Содержание</t>
   </si>
@@ -1003,6 +1003,9 @@
   </si>
   <si>
     <t>Сравнение конкретного файла в разных коммитах</t>
+  </si>
+  <si>
+    <t>О ветвлении в двух словах</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1334,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N194"/>
+  <dimension ref="A1:N195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="3.140625" customWidth="1"/>
@@ -3366,6 +3369,14 @@
         <v>318</v>
       </c>
     </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195">
+        <v>66</v>
+      </c>
+      <c r="E195" t="s">
+        <v>326</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ProGit/Commands.xlsx
+++ b/ProGit/Commands.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Git\ProGit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F45443-FA4F-4104-BDFC-73941D1D17FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4DD83E-FF9D-471B-8AAA-6AEEDD032CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="2505" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="311">
   <si>
     <t>Содержание</t>
   </si>
@@ -904,6 +904,60 @@
   </si>
   <si>
     <t>git config --global alias.(co) (checkout)</t>
+  </si>
+  <si>
+    <t>Создание новой ветки</t>
+  </si>
+  <si>
+    <t>git branch (feature)</t>
+  </si>
+  <si>
+    <t>git log --decorate</t>
+  </si>
+  <si>
+    <t>Узнать, куда указывают указатели веток</t>
+  </si>
+  <si>
+    <t>Переглючение веток</t>
+  </si>
+  <si>
+    <t>git checkout (feature)</t>
+  </si>
+  <si>
+    <t>Переключение на указанную ветку</t>
+  </si>
+  <si>
+    <t>git log (develop)</t>
+  </si>
+  <si>
+    <t>Вывод информации по указанной ветке</t>
+  </si>
+  <si>
+    <t>git log --all</t>
+  </si>
+  <si>
+    <t>Вывод информации по всем веткам</t>
+  </si>
+  <si>
+    <t>git log --oneline --decorate --graph --all</t>
+  </si>
+  <si>
+    <t>Отображение истории коммитов, текущего положения указателей веток и истории ветвления</t>
+  </si>
+  <si>
+    <t>git switch (develop)</t>
+  </si>
+  <si>
+    <t>git switch -c (new-branch)</t>
+  </si>
+  <si>
+    <t>git switch --create (new-branch)</t>
+  </si>
+  <si>
+    <t>git switch -</t>
+  </si>
+  <si>
+    <t>Возврат к предыдущей извлеченной ветке</t>
   </si>
 </sst>
 </file>
@@ -1232,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I192"/>
+  <dimension ref="A1:I204"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="3.140625" customWidth="1"/>
@@ -2652,6 +2706,96 @@
         <v>184</v>
       </c>
     </row>
+    <row r="193" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F193" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="194" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G194" t="s">
+        <v>294</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="195" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G195" t="s">
+        <v>295</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="196" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F196" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="197" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G197" t="s">
+        <v>298</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="198" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G198" t="s">
+        <v>300</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="199" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G199" t="s">
+        <v>302</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="200" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G200" t="s">
+        <v>304</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="201" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G201" t="s">
+        <v>306</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="202" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G202" t="s">
+        <v>307</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="203" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G203" t="s">
+        <v>308</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="204" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G204" t="s">
+        <v>309</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ProGit/Commands.xlsx
+++ b/ProGit/Commands.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Git\ProGit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4DD83E-FF9D-471B-8AAA-6AEEDD032CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989D28CD-CED2-4B15-A6E9-4E6C9FBA34D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="2505" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="367">
   <si>
     <t>Содержание</t>
   </si>
@@ -909,6 +909,9 @@
     <t>Создание новой ветки</t>
   </si>
   <si>
+    <t>git branch</t>
+  </si>
+  <si>
     <t>git branch (feature)</t>
   </si>
   <si>
@@ -958,6 +961,171 @@
   </si>
   <si>
     <t>Возврат к предыдущей извлеченной ветке</t>
+  </si>
+  <si>
+    <t>Основы ветвления и слияния</t>
+  </si>
+  <si>
+    <t>git merge (hotfix)</t>
+  </si>
+  <si>
+    <t>Слияние указанной ветки в текущую</t>
+  </si>
+  <si>
+    <t>git branch -d (hotfix)</t>
+  </si>
+  <si>
+    <t>Удаление указанной ветки</t>
+  </si>
+  <si>
+    <t>Основы слияния</t>
+  </si>
+  <si>
+    <t>Основные конфликты слияния</t>
+  </si>
+  <si>
+    <t>git mergetool</t>
+  </si>
+  <si>
+    <t>Использование графического инструмента для разрешения конфликтов</t>
+  </si>
+  <si>
+    <t>git mergetool (opendiff)</t>
+  </si>
+  <si>
+    <t>Использование конкретного графического инструмента для разрешения конфликтов</t>
+  </si>
+  <si>
+    <t>Управление ветками</t>
+  </si>
+  <si>
+    <t>Показать список локальных веток</t>
+  </si>
+  <si>
+    <t>git branch -v</t>
+  </si>
+  <si>
+    <t>Просмотр последних коммитов на каждой ветке</t>
+  </si>
+  <si>
+    <t>git branch --merged</t>
+  </si>
+  <si>
+    <t>git branch --no-merged</t>
+  </si>
+  <si>
+    <t>Список веток, слитых с текущей</t>
+  </si>
+  <si>
+    <t>Список веток, не слитых с текущей</t>
+  </si>
+  <si>
+    <t>git branch -d (feature)</t>
+  </si>
+  <si>
+    <t>Удаление слитой ветки</t>
+  </si>
+  <si>
+    <t>git branch -D (feature)</t>
+  </si>
+  <si>
+    <t>Принудительное удаление не слитой ветки</t>
+  </si>
+  <si>
+    <t>git branch --merged (main)</t>
+  </si>
+  <si>
+    <t>git branch --no-merged (main)</t>
+  </si>
+  <si>
+    <t>Список веток, слитых с указанной</t>
+  </si>
+  <si>
+    <t>Список веток, не слитых с указанной</t>
+  </si>
+  <si>
+    <t>Переименование ветки</t>
+  </si>
+  <si>
+    <t>git branch --move (bad-name) (corrected-name)</t>
+  </si>
+  <si>
+    <t>git push --set-upstream (origin) (corrected-name)</t>
+  </si>
+  <si>
+    <t>Отправка переименованной ветки на удаленный сервер</t>
+  </si>
+  <si>
+    <t>git push (origin) --delete (bad-name)</t>
+  </si>
+  <si>
+    <t>Удаление ветки с удаленного сервера</t>
+  </si>
+  <si>
+    <t>git branch --all</t>
+  </si>
+  <si>
+    <t>Просмотр всех веток, включая ветки всех подключенных удаленных серверов</t>
+  </si>
+  <si>
+    <t>Работа с ветками</t>
+  </si>
+  <si>
+    <t>Долгоживущие ветки</t>
+  </si>
+  <si>
+    <t>Тематические ветки</t>
+  </si>
+  <si>
+    <t>Удаленные ветки</t>
+  </si>
+  <si>
+    <t>git ls-remote (origin)</t>
+  </si>
+  <si>
+    <t>Полный список ссылок удаленного сервера</t>
+  </si>
+  <si>
+    <t>Список удаленных веток и дополнительной информации</t>
+  </si>
+  <si>
+    <t>git show (origin/main)</t>
+  </si>
+  <si>
+    <t>Просмотр коммита, на который указывает локальный указатель удаленной ветки</t>
+  </si>
+  <si>
+    <t>git fetch (origin)</t>
+  </si>
+  <si>
+    <t>Скачивание всех отсутствующий в локальном репозитории файлов с удаленного сервера</t>
+  </si>
+  <si>
+    <t>Отправка изменений</t>
+  </si>
+  <si>
+    <t>git push (origin) (feature)</t>
+  </si>
+  <si>
+    <t>Отправка ветки на удаленный сервер</t>
+  </si>
+  <si>
+    <t>git push (origin) (feature):(remote-feature)</t>
+  </si>
+  <si>
+    <t>Отправка ветки на удаленный сервер под другим именем</t>
+  </si>
+  <si>
+    <t>git config --global credential.helper cache</t>
+  </si>
+  <si>
+    <t>Позволяет не вводить свои данные каждый раз при отправке информации на удаленный сервер</t>
+  </si>
+  <si>
+    <t>git checkout -b (serverfix) (origin/serverfix)</t>
+  </si>
+  <si>
+    <t>Отслеживание веток</t>
   </si>
 </sst>
 </file>
@@ -1286,12 +1454,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I204"/>
+  <dimension ref="A1:I239"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="3.140625" customWidth="1"/>
     <col min="7" max="7" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="90.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2706,94 +2874,351 @@
         <v>184</v>
       </c>
     </row>
-    <row r="193" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F193" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="194" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G194" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="195" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G195" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="196" spans="6:8" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F196" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="197" spans="6:8" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G197" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="198" spans="6:8" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G198" t="s">
+        <v>301</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G199" t="s">
+        <v>303</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G200" t="s">
+        <v>305</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G201" t="s">
+        <v>307</v>
+      </c>
+      <c r="H201" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="H198" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="199" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="G199" t="s">
-        <v>302</v>
-      </c>
-      <c r="H199" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="200" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="G200" t="s">
-        <v>304</v>
-      </c>
-      <c r="H200" s="1" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="201" spans="6:8" x14ac:dyDescent="0.25">
-      <c r="G201" t="s">
-        <v>306</v>
-      </c>
-      <c r="H201" s="1" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="202" spans="6:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G202" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H202" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="203" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G203" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H203" s="1" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="204" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G204" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205">
+        <v>73</v>
+      </c>
+      <c r="E205" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G206" t="s">
+        <v>313</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G207" t="s">
+        <v>315</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F208" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F209" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G210" t="s">
+        <v>319</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G211" t="s">
+        <v>321</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212">
+        <v>82</v>
+      </c>
+      <c r="E212" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G213" t="s">
+        <v>294</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G214" t="s">
+        <v>325</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G215" t="s">
+        <v>327</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G216" t="s">
+        <v>328</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G217" t="s">
+        <v>335</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G218" t="s">
+        <v>336</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G219" t="s">
+        <v>331</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G220" t="s">
+        <v>333</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F221" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G222" t="s">
+        <v>340</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G223" t="s">
+        <v>341</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G224" t="s">
+        <v>343</v>
+      </c>
+      <c r="H224" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G225" t="s">
+        <v>345</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226">
+        <v>86</v>
+      </c>
+      <c r="E226" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F227" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F228" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229">
+        <v>89</v>
+      </c>
+      <c r="E229" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G230" t="s">
+        <v>351</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G231" t="s">
+        <v>272</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G232" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G233" t="s">
+        <v>356</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F234" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G235" t="s">
+        <v>359</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G236" t="s">
+        <v>361</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G237" t="s">
+        <v>363</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G238" t="s">
+        <v>365</v>
+      </c>
+      <c r="H238" s="2"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F239" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/ProGit/Commands.xlsx
+++ b/ProGit/Commands.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Git\ProGit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989D28CD-CED2-4B15-A6E9-4E6C9FBA34D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F74D6FC-7FFB-4986-B743-8AB793562F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="2505" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="396">
   <si>
     <t>Содержание</t>
   </si>
@@ -567,12 +567,6 @@
     <t>Ветвление в Git</t>
   </si>
   <si>
-    <t>Скачивание всех изменений с конкретного удаленного репозитория</t>
-  </si>
-  <si>
-    <t>Скачивание всех изменений с единственного удаленного репозитория</t>
-  </si>
-  <si>
     <t>Сравнение двух коммитов</t>
   </si>
   <si>
@@ -1098,9 +1092,6 @@
     <t>git fetch (origin)</t>
   </si>
   <si>
-    <t>Скачивание всех отсутствующий в локальном репозитории файлов с удаленного сервера</t>
-  </si>
-  <si>
     <t>Отправка изменений</t>
   </si>
   <si>
@@ -1126,6 +1117,102 @@
   </si>
   <si>
     <t>Отслеживание веток</t>
+  </si>
+  <si>
+    <t>git checkout --track (origin/serverfix)</t>
+  </si>
+  <si>
+    <t>git checkout (serverfix)</t>
+  </si>
+  <si>
+    <t>git checkout -b (sf) (origin/serverfix)</t>
+  </si>
+  <si>
+    <t>git branch -u (origin/serverfix)</t>
+  </si>
+  <si>
+    <t>git branch --set-upstream-to (origin/serverfix)</t>
+  </si>
+  <si>
+    <t>git merge @{upstream}</t>
+  </si>
+  <si>
+    <t>git merge @{u}</t>
+  </si>
+  <si>
+    <t>git branch -vv</t>
+  </si>
+  <si>
+    <t>Просмотр настройки веток слежения и дополнительная информация</t>
+  </si>
+  <si>
+    <t>Создание и переход на ветку слежения</t>
+  </si>
+  <si>
+    <t>Создание и переход на ветку слежения с отличным названием локальной ветки слежения</t>
+  </si>
+  <si>
+    <t>Настройка текущей локальной ветки на слежение за указанной удаленной</t>
+  </si>
+  <si>
+    <t>git fetch --all; git branch -vv</t>
+  </si>
+  <si>
+    <t>Получение данных со всех удаленных серверов и получение актуальной информации по веткам слежения</t>
+  </si>
+  <si>
+    <t>Получение изменений</t>
+  </si>
+  <si>
+    <t>Скачивание всех изменений с конкретного удаленного репозитория без слияния</t>
+  </si>
+  <si>
+    <t>Скачивание всех изменений с единственного удаленного репозитория без слияния</t>
+  </si>
+  <si>
+    <t>Скачивание всех отсутствующий в локальном репозитории файлов с удаленного сервера без слияния</t>
+  </si>
+  <si>
+    <t>Удаление веток на удаленном сервере</t>
+  </si>
+  <si>
+    <t>git push origin --delete (serverfix)</t>
+  </si>
+  <si>
+    <t>Удаление указателя ветки с удаленного сервера</t>
+  </si>
+  <si>
+    <t>Перебазирование</t>
+  </si>
+  <si>
+    <t>Простейшее перебазирование</t>
+  </si>
+  <si>
+    <t>git merge (origin/serverfix)</t>
+  </si>
+  <si>
+    <t>git rebase (main)</t>
+  </si>
+  <si>
+    <t>Перенос текущей ветки поверх указанной</t>
+  </si>
+  <si>
+    <t>Более интересные перемещения</t>
+  </si>
+  <si>
+    <t>git rebase --onto (main) (develop) (feature)</t>
+  </si>
+  <si>
+    <t>git rebase (main) (develop)</t>
+  </si>
+  <si>
+    <t>Перенос второй указанной ветки поверх первой указанной ветки</t>
+  </si>
+  <si>
+    <t>Опасности перемещения</t>
+  </si>
+  <si>
+    <t>Меняя базу, меняй основание</t>
   </si>
 </sst>
 </file>
@@ -1454,12 +1541,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I239"/>
+  <dimension ref="A1:I260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="3.140625" customWidth="1"/>
     <col min="7" max="7" width="53.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="102" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1633,7 +1720,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G25" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>36</v>
@@ -1651,7 +1738,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G28" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>37</v>
@@ -1675,7 +1762,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G31" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>40</v>
@@ -1683,7 +1770,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G32" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="H32" s="1" t="s">
         <v>41</v>
@@ -1691,7 +1778,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G33" s="1" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>42</v>
@@ -1702,7 +1789,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G34" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>44</v>
@@ -1716,7 +1803,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G36" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>45</v>
@@ -1724,7 +1811,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G37" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>46</v>
@@ -1737,7 +1824,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G39" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H39" s="1" t="s">
         <v>47</v>
@@ -1758,7 +1845,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G42" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>50</v>
@@ -1771,7 +1858,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G44" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>51</v>
@@ -1779,7 +1866,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G45" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H45" s="1" t="s">
         <v>52</v>
@@ -1795,7 +1882,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G47" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H47" s="1" t="s">
         <v>53</v>
@@ -1803,7 +1890,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G48" s="1" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>53</v>
@@ -1811,7 +1898,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G49" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>54</v>
@@ -1827,7 +1914,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G51" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>55</v>
@@ -1864,7 +1951,7 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G56" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>64</v>
@@ -1872,7 +1959,7 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G57" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>65</v>
@@ -1914,7 +2001,7 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G63" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>133</v>
@@ -1922,7 +2009,7 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G64" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H64" s="1" t="s">
         <v>133</v>
@@ -1948,7 +2035,7 @@
     </row>
     <row r="68" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G68" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>72</v>
@@ -1956,7 +2043,7 @@
     </row>
     <row r="69" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G69" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>72</v>
@@ -1982,7 +2069,7 @@
     </row>
     <row r="73" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G73" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>76</v>
@@ -1990,7 +2077,7 @@
     </row>
     <row r="74" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G74" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>76</v>
@@ -1998,18 +2085,18 @@
     </row>
     <row r="75" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G75" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="76" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G76" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="6:8" x14ac:dyDescent="0.25">
@@ -2019,7 +2106,7 @@
     </row>
     <row r="78" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G78" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H78" s="1" t="s">
         <v>79</v>
@@ -2027,7 +2114,7 @@
     </row>
     <row r="79" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G79" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H79" s="1" t="s">
         <v>80</v>
@@ -2040,7 +2127,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G81" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H81" s="1" t="s">
         <v>82</v>
@@ -2048,7 +2135,7 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G82" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H82" s="1" t="s">
         <v>83</v>
@@ -2061,7 +2148,7 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G84" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H84" s="1" t="s">
         <v>87</v>
@@ -2069,7 +2156,7 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G85" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H85" s="1" t="s">
         <v>85</v>
@@ -2077,7 +2164,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G86" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>86</v>
@@ -2090,7 +2177,7 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G88" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>89</v>
@@ -2114,7 +2201,7 @@
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G91" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H91" s="1" t="s">
         <v>92</v>
@@ -2122,7 +2209,7 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G92" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H92" s="1" t="s">
         <v>92</v>
@@ -2130,7 +2217,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G93" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>93</v>
@@ -2138,7 +2225,7 @@
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G94" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H94" s="1" t="s">
         <v>94</v>
@@ -2146,7 +2233,7 @@
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G95" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="H95" s="1" t="s">
         <v>95</v>
@@ -2154,7 +2241,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G96" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H96" s="1" t="s">
         <v>96</v>
@@ -2162,7 +2249,7 @@
     </row>
     <row r="97" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G97" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="H97" s="1" t="s">
         <v>98</v>
@@ -2170,7 +2257,7 @@
     </row>
     <row r="98" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G98" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H98" s="1" t="s">
         <v>99</v>
@@ -2178,7 +2265,7 @@
     </row>
     <row r="99" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G99" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>100</v>
@@ -2186,7 +2273,7 @@
     </row>
     <row r="100" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G100" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>97</v>
@@ -2194,7 +2281,7 @@
     </row>
     <row r="101" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G101" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="H101" s="1" t="s">
         <v>101</v>
@@ -2202,7 +2289,7 @@
     </row>
     <row r="102" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G102" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>102</v>
@@ -2210,7 +2297,7 @@
     </row>
     <row r="103" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G103" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>103</v>
@@ -2218,7 +2305,7 @@
     </row>
     <row r="104" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G104" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>104</v>
@@ -2226,7 +2313,7 @@
     </row>
     <row r="105" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G105" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H105" s="1" t="s">
         <v>105</v>
@@ -2234,7 +2321,7 @@
     </row>
     <row r="106" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G106" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>106</v>
@@ -2242,7 +2329,7 @@
     </row>
     <row r="107" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G107" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H107" s="1" t="s">
         <v>107</v>
@@ -2250,7 +2337,7 @@
     </row>
     <row r="108" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G108" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="H108" s="1" t="s">
         <v>108</v>
@@ -2258,7 +2345,7 @@
     </row>
     <row r="109" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G109" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>109</v>
@@ -2266,7 +2353,7 @@
     </row>
     <row r="110" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G110" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H110" s="1" t="s">
         <v>110</v>
@@ -2274,7 +2361,7 @@
     </row>
     <row r="111" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G111" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="H111" s="1" t="s">
         <v>111</v>
@@ -2282,7 +2369,7 @@
     </row>
     <row r="112" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G112" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>112</v>
@@ -2290,7 +2377,7 @@
     </row>
     <row r="113" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G113" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>113</v>
@@ -2298,7 +2385,7 @@
     </row>
     <row r="114" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G114" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="H114" s="1" t="s">
         <v>114</v>
@@ -2306,7 +2393,7 @@
     </row>
     <row r="115" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G115" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>0</v>
@@ -2314,7 +2401,7 @@
     </row>
     <row r="116" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G116" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="H116" s="1" t="s">
         <v>115</v>
@@ -2322,7 +2409,7 @@
     </row>
     <row r="117" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G117" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H117" s="1" t="s">
         <v>116</v>
@@ -2330,7 +2417,7 @@
     </row>
     <row r="118" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G118" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="H118" s="1" t="s">
         <v>117</v>
@@ -2338,7 +2425,7 @@
     </row>
     <row r="119" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G119" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="H119" s="1" t="s">
         <v>118</v>
@@ -2346,7 +2433,7 @@
     </row>
     <row r="120" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G120" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>119</v>
@@ -2354,7 +2441,7 @@
     </row>
     <row r="121" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G121" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>120</v>
@@ -2367,7 +2454,7 @@
     </row>
     <row r="123" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G123" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H123" s="1" t="s">
         <v>93</v>
@@ -2375,7 +2462,7 @@
     </row>
     <row r="124" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G124" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>122</v>
@@ -2383,7 +2470,7 @@
     </row>
     <row r="125" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G125" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>122</v>
@@ -2391,7 +2478,7 @@
     </row>
     <row r="126" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G126" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="H126" s="1" t="s">
         <v>123</v>
@@ -2399,7 +2486,7 @@
     </row>
     <row r="127" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G127" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H127" s="1" t="s">
         <v>123</v>
@@ -2407,7 +2494,7 @@
     </row>
     <row r="128" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G128" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H128" s="1" t="s">
         <v>124</v>
@@ -2415,7 +2502,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G129" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="H129" s="1" t="s">
         <v>126</v>
@@ -2423,7 +2510,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G130" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H130" s="1" t="s">
         <v>125</v>
@@ -2431,7 +2518,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G131" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>125</v>
@@ -2439,7 +2526,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G132" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>127</v>
@@ -2447,7 +2534,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G133" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="H133" s="1" t="s">
         <v>128</v>
@@ -2455,7 +2542,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G134" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H134" s="1" t="s">
         <v>129</v>
@@ -2471,7 +2558,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G136" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="H136" s="1" t="s">
         <v>131</v>
@@ -2484,7 +2571,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G138" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H138" s="1" t="s">
         <v>134</v>
@@ -2497,7 +2584,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G140" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="H140" s="3" t="s">
         <v>137</v>
@@ -2510,7 +2597,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G142" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>134</v>
@@ -2518,7 +2605,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G143" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H143" s="1" t="s">
         <v>137</v>
@@ -2547,7 +2634,7 @@
     </row>
     <row r="147" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G147" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>141</v>
@@ -2560,7 +2647,7 @@
     </row>
     <row r="149" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G149" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="H149" s="1" t="s">
         <v>143</v>
@@ -2573,10 +2660,10 @@
     </row>
     <row r="151" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G151" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>180</v>
+        <v>379</v>
       </c>
     </row>
     <row r="152" spans="6:8" x14ac:dyDescent="0.25">
@@ -2584,12 +2671,12 @@
         <v>144</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>181</v>
+        <v>380</v>
       </c>
     </row>
     <row r="153" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G153" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H153" s="1" t="s">
         <v>147</v>
@@ -2597,7 +2684,7 @@
     </row>
     <row r="154" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G154" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="H154" s="1" t="s">
         <v>146</v>
@@ -2610,7 +2697,7 @@
     </row>
     <row r="156" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G156" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H156" s="1" t="s">
         <v>149</v>
@@ -2623,7 +2710,7 @@
     </row>
     <row r="158" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G158" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H158" s="1" t="s">
         <v>151</v>
@@ -2636,7 +2723,7 @@
     </row>
     <row r="160" spans="6:8" x14ac:dyDescent="0.25">
       <c r="G160" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H160" s="1" t="s">
         <v>153</v>
@@ -2644,7 +2731,7 @@
     </row>
     <row r="161" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G161" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H161" s="1" t="s">
         <v>154</v>
@@ -2652,7 +2739,7 @@
     </row>
     <row r="162" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G162" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="H162" s="1" t="s">
         <v>154</v>
@@ -2678,7 +2765,7 @@
     </row>
     <row r="166" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G166" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H166" s="1" t="s">
         <v>158</v>
@@ -2686,7 +2773,7 @@
     </row>
     <row r="167" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G167" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="H167" s="1" t="s">
         <v>158</v>
@@ -2704,7 +2791,7 @@
     </row>
     <row r="170" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G170" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="H170" s="1" t="s">
         <v>161</v>
@@ -2712,7 +2799,7 @@
     </row>
     <row r="171" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G171" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H171" s="1" t="s">
         <v>162</v>
@@ -2720,7 +2807,7 @@
     </row>
     <row r="172" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G172" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="H172" s="1" t="s">
         <v>163</v>
@@ -2733,7 +2820,7 @@
     </row>
     <row r="174" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G174" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>167</v>
@@ -2746,7 +2833,7 @@
     </row>
     <row r="176" spans="5:8" x14ac:dyDescent="0.25">
       <c r="G176" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="H176" s="1" t="s">
         <v>166</v>
@@ -2759,7 +2846,7 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G178" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H178" s="1" t="s">
         <v>169</v>
@@ -2767,7 +2854,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G179" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>170</v>
@@ -2775,7 +2862,7 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G180" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H180" s="1" t="s">
         <v>171</v>
@@ -2788,7 +2875,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G182" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H182" s="1" t="s">
         <v>173</v>
@@ -2796,7 +2883,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G183" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>174</v>
@@ -2804,7 +2891,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G184" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>174</v>
@@ -2817,7 +2904,7 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G186" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H186" s="1" t="s">
         <v>176</v>
@@ -2825,10 +2912,10 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G187" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
@@ -2841,7 +2928,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G189" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>178</v>
@@ -2871,97 +2958,97 @@
         <v>66</v>
       </c>
       <c r="E192" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F193" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G194" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H194" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G195" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F196" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G197" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G198" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H198" s="1" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G199" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G200" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H200" s="1" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G201" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G202" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G203" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="H203" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G204" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -2969,49 +3056,49 @@
         <v>73</v>
       </c>
       <c r="E205" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G206" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H206" s="1" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G207" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F208" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F209" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G210" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="H210" s="1" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G211" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H211" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -3019,108 +3106,108 @@
         <v>82</v>
       </c>
       <c r="E212" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G213" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G214" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H214" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G215" t="s">
+        <v>325</v>
+      </c>
+      <c r="H215" s="1" t="s">
         <v>327</v>
-      </c>
-      <c r="H215" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G216" t="s">
+        <v>326</v>
+      </c>
+      <c r="H216" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="H216" s="1" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G217" t="s">
+        <v>333</v>
+      </c>
+      <c r="H217" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="H217" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G218" t="s">
+        <v>334</v>
+      </c>
+      <c r="H218" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="H218" s="1" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G219" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H219" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G220" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="H220" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F221" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G222" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H222" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G223" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G224" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H224" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G225" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H225" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
@@ -3128,17 +3215,17 @@
         <v>86</v>
       </c>
       <c r="E226" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F227" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F228" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
@@ -3146,79 +3233,223 @@
         <v>89</v>
       </c>
       <c r="E229" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G230" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G231" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="H231" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G232" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G233" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H233" s="1" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F234" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G235" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G236" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="H236" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G237" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G238" t="s">
-        <v>365</v>
-      </c>
-      <c r="H238" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="H238" s="3" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F239" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G240" t="s">
+        <v>364</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G241" t="s">
+        <v>365</v>
+      </c>
+      <c r="H241" s="2" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G242" t="s">
         <v>366</v>
+      </c>
+      <c r="H242" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G243" t="s">
+        <v>367</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G244" t="s">
+        <v>368</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G245" t="s">
+        <v>369</v>
+      </c>
+      <c r="H245" s="2"/>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G246" t="s">
+        <v>370</v>
+      </c>
+      <c r="H246" s="2"/>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G247" t="s">
+        <v>371</v>
+      </c>
+      <c r="H247" s="1" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G248" t="s">
+        <v>376</v>
+      </c>
+      <c r="H248" s="1" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G249" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="H249" s="2"/>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F250" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F251" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G252" t="s">
+        <v>383</v>
+      </c>
+      <c r="H252" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253">
+        <v>99</v>
+      </c>
+      <c r="E253" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F254" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G255" t="s">
+        <v>388</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F256" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="257" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G257" t="s">
+        <v>391</v>
+      </c>
+      <c r="H257" s="2"/>
+    </row>
+    <row r="258" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="G258" t="s">
+        <v>392</v>
+      </c>
+      <c r="H258" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="259" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F259" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="260" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F260" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/ProGit/Commands.xlsx
+++ b/ProGit/Commands.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Git\ProGit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F74D6FC-7FFB-4986-B743-8AB793562F99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD9E95D-DCEF-4372-8CA2-9396FCE0169C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-25320" yWindow="2505" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="401">
   <si>
     <t>Содержание</t>
   </si>
@@ -1213,6 +1213,21 @@
   </si>
   <si>
     <t>Меняя базу, меняй основание</t>
+  </si>
+  <si>
+    <t>git pull --rabase (origin) (main)</t>
+  </si>
+  <si>
+    <t>Должен решить проблему с перебазированием на удаленном сервере</t>
+  </si>
+  <si>
+    <t>git config --global pull.rebase true</t>
+  </si>
+  <si>
+    <t>Автоматическое перебазирование при скачивании с удаленного сервера</t>
+  </si>
+  <si>
+    <t>Перемещение vs. слияние</t>
   </si>
 </sst>
 </file>
@@ -1541,10 +1556,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I260"/>
+  <dimension ref="A1:I264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="3.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="3.140625" customWidth="1"/>
     <col min="7" max="7" width="53.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="102" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.7109375" bestFit="1" customWidth="1"/>
@@ -3428,13 +3444,13 @@
         <v>390</v>
       </c>
     </row>
-    <row r="257" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G257" t="s">
         <v>391</v>
       </c>
       <c r="H257" s="2"/>
     </row>
-    <row r="258" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G258" t="s">
         <v>392</v>
       </c>
@@ -3442,14 +3458,43 @@
         <v>393</v>
       </c>
     </row>
-    <row r="259" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F259" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="260" spans="6:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F260" t="s">
         <v>395</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G261" t="s">
+        <v>396</v>
+      </c>
+      <c r="H261" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G262" t="s">
+        <v>398</v>
+      </c>
+      <c r="H262" s="2" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F263" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264">
+        <v>109</v>
+      </c>
+      <c r="D264" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
